--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G5">
@@ -1120,68 +1120,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:00:00</t>
+          <t>2026-08-25 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-25 13:05:00</t>
+          <t>2026-08-25 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:10:00</t>
+          <t>2026-08-25 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-25 13:45:00</t>
+          <t>2026-08-25 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-25 14:00:00</t>
+          <t>2026-08-25 13:05:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-25 14:00:00</t>
+          <t>2026-08-25 13:10:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-25 14:30:00</t>
+          <t>2026-08-25 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-25 14:30:00</t>
+          <t>2026-08-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-08-25 14:30:00</t>
+          <t>2026-08-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-25 15:00:00</t>
+          <t>2026-08-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-25 15:00:00</t>
+          <t>2026-08-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-25 16:00:00</t>
+          <t>2026-08-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-25 16:00:00</t>
+          <t>2026-08-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-25 16:00:00</t>
+          <t>2026-08-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,68 +3891,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:00:00</t>
+          <t>2026-08-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:30:00</t>
+          <t>2026-08-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:30:00</t>
+          <t>2026-08-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,156 +4337,645 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>2.3</v>
+      </c>
+      <c r="O25">
+        <v>2.73</v>
+      </c>
+      <c r="P25">
+        <v>3.13</v>
+      </c>
+      <c r="Q25">
+        <v>3.1</v>
+      </c>
+      <c r="R25">
+        <v>1.77</v>
+      </c>
+      <c r="S25">
+        <v>1.61</v>
+      </c>
+      <c r="T25">
+        <v>2.25</v>
+      </c>
+      <c r="U25">
+        <v>3.8</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.09</v>
+      </c>
+      <c r="Y25">
+        <v>1.58</v>
+      </c>
+      <c r="Z25">
+        <v>2.27</v>
+      </c>
+      <c r="AA25">
+        <v>2.62</v>
+      </c>
+      <c r="AB25">
+        <v>1.38</v>
+      </c>
+      <c r="AC25">
+        <v>5.15</v>
+      </c>
+      <c r="AD25">
+        <v>1.1</v>
+      </c>
+      <c r="AE25">
+        <v>1.03</v>
+      </c>
+      <c r="AF25">
+        <v>2.17</v>
+      </c>
+      <c r="AG25">
+        <v>1.6</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.35</v>
+      </c>
+      <c r="AK25">
+        <v>1.5</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-08-25 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-08-25 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-08-25 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Universitario de Vinto</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
         </is>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-08-25 20:00:00</t>
         </is>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G22">

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>4.37</v>
+        <v>4.79</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -1468,10 +1468,10 @@
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1480,34 +1480,34 @@
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
         <v>3.3</v>
       </c>
       <c r="AA7">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AC7">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -4227,37 +4227,37 @@
         <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA24">
         <v>2</v>
@@ -4266,19 +4266,19 @@
         <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD24">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O25">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P25">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
       </c>
       <c r="R25">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="S25">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.09</v>
       </c>
       <c r="Y25">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z25">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB25">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC25">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AD25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
         <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1453,10 +1453,10 @@
         <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.79</v>
+        <v>3.8</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O9">
         <v>3.7</v>
@@ -1788,22 +1788,22 @@
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1818,22 +1818,22 @@
         <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC9">
         <v>2.23</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,43 +2265,43 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA12">
         <v>1.75</v>
@@ -2310,19 +2310,19 @@
         <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
         <v>1.37</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -3747,19 +3747,19 @@
         <v>2.45</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,10 +3768,10 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="AA21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB21">
         <v>2.25</v>
@@ -3780,16 +3780,16 @@
         <v>2.45</v>
       </c>
       <c r="AD21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF21">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P22">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R22">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="U22">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V22">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA22">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB22">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AC22">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AD22">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AF22">
         <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
         <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
         <v>3</v>
@@ -4556,43 +4556,43 @@
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R26">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U26">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
         <v>1.1</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z26">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA26">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AB26">
         <v>1.53</v>
       </c>
       <c r="AC26">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AD26">
         <v>1.17</v>
@@ -4601,7 +4601,7 @@
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG26">
         <v>1.67</v>
@@ -4620,7 +4620,7 @@
         <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4725,16 +4725,16 @@
         <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4743,19 +4743,19 @@
         <v>1.08</v>
       </c>
       <c r="Y27">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB27">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD27">
         <v>1.22</v>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
         <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2446,13 +2446,13 @@
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="U13">
         <v>2.62</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB13">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC13">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AK13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="O14">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="Q14">
         <v>2.05</v>
       </c>
       <c r="R14">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
         <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
+        <v>2.3</v>
+      </c>
+      <c r="AC14">
         <v>2.38</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
+        <v>1.53</v>
+      </c>
+      <c r="AE14">
+        <v>1.22</v>
+      </c>
+      <c r="AF14">
+        <v>1.57</v>
+      </c>
+      <c r="AG14">
+        <v>2.25</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.18</v>
+      </c>
+      <c r="AK14">
         <v>2.3</v>
-      </c>
-      <c r="AD14">
-        <v>1.52</v>
-      </c>
-      <c r="AE14">
-        <v>1.19</v>
-      </c>
-      <c r="AF14">
-        <v>1.54</v>
-      </c>
-      <c r="AG14">
-        <v>2.23</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.22</v>
-      </c>
-      <c r="AK14">
-        <v>2.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>3.1</v>
       </c>
       <c r="R25">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S25">
         <v>1.53</v>
@@ -4457,7 +4457,7 @@
         <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1800,10 +1800,10 @@
         <v>2.29</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,10 +1812,10 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
         <v>2.38</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.09</v>
@@ -1812,7 +1812,7 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
         <v>1.53</v>
@@ -1833,7 +1833,7 @@
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
         <v>1.84</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>3.8</v>
+        <v>4.79</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
         <v>3.75</v>
@@ -2286,7 +2286,7 @@
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2298,19 +2298,19 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
         <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="AD12">
         <v>1.37</v>
@@ -2319,10 +2319,10 @@
         <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -2482,10 +2482,10 @@
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,46 +2591,46 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q14">
         <v>2.05</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
         <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
         <v>2.3</v>
@@ -2642,13 +2642,13 @@
         <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P21">
         <v>3.25</v>
@@ -3744,7 +3744,7 @@
         <v>2.25</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
         <v>1.24</v>
@@ -3759,13 +3759,13 @@
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
         <v>4.76</v>
@@ -3774,22 +3774,22 @@
         <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AC21">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
         <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,19 +3910,19 @@
         <v>2.75</v>
       </c>
       <c r="S22">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V22">
         <v>1.93</v>
       </c>
       <c r="W22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3940,19 +3940,19 @@
         <v>3.18</v>
       </c>
       <c r="AC22">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O24">
         <v>3.3</v>
@@ -4236,7 +4236,7 @@
         <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
         <v>2.75</v>
@@ -4269,16 +4269,16 @@
         <v>3.1</v>
       </c>
       <c r="AD24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>3.1</v>
       </c>
       <c r="R25">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="S25">
         <v>1.53</v>
@@ -4408,10 +4408,10 @@
         <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.09</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,43 +4547,43 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
         <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="R26">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
         <v>2.33</v>
       </c>
       <c r="U26">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z26">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AA26">
         <v>2.54</v>
@@ -4595,7 +4595,7 @@
         <v>4.9</v>
       </c>
       <c r="AD26">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
@@ -4722,49 +4722,49 @@
         <v>2.5</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U27">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V27">
         <v>1.29</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
         <v>1.08</v>
       </c>
       <c r="Y27">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z27">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AA27">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC27">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
         <v>1.73</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q2">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S2">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AB2">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
       <c r="AD2">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3">
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>4.03</v>
+        <v>3.17</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
+        <v>1.04</v>
+      </c>
+      <c r="Y3">
+        <v>1.41</v>
+      </c>
+      <c r="Z3">
+        <v>2.54</v>
+      </c>
+      <c r="AA3">
+        <v>2.38</v>
+      </c>
+      <c r="AB3">
+        <v>1.56</v>
+      </c>
+      <c r="AC3">
+        <v>3.9</v>
+      </c>
+      <c r="AD3">
+        <v>1.19</v>
+      </c>
+      <c r="AE3">
         <v>1.01</v>
       </c>
-      <c r="Y3">
-        <v>1.29</v>
-      </c>
-      <c r="Z3">
-        <v>3.4</v>
-      </c>
-      <c r="AA3">
-        <v>1.92</v>
-      </c>
-      <c r="AB3">
-        <v>1.85</v>
-      </c>
-      <c r="AC3">
-        <v>3.24</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
       <c r="AF3">
+        <v>1.97</v>
+      </c>
+      <c r="AG3">
         <v>1.73</v>
       </c>
-      <c r="AG3">
-        <v>2</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,34 +964,34 @@
         <v>1.53</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.24</v>
@@ -1000,25 +1000,25 @@
         <v>3.38</v>
       </c>
       <c r="AA4">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AB4">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>4.79</v>
+        <v>4.45</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
         <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
         <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
         <v>1.53</v>
@@ -1833,7 +1833,7 @@
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q12">
         <v>2.38</v>
@@ -2283,10 +2283,10 @@
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2298,22 +2298,22 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
         <v>1.12</v>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -2446,13 +2446,13 @@
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U13">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2476,16 +2476,16 @@
         <v>2.95</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK13">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="Q14">
         <v>2.05</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
         <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
         <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2627,7 +2627,7 @@
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
         <v>1.55</v>
@@ -2639,16 +2639,16 @@
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE14">
         <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O21">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="P21">
         <v>3.25</v>
@@ -3744,7 +3744,7 @@
         <v>2.25</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
         <v>1.24</v>
@@ -3759,37 +3759,37 @@
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
         <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AC21">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AD21">
         <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
         <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O22">
         <v>4.8</v>
@@ -3904,10 +3904,10 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R22">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="S22">
         <v>1.2</v>
@@ -3916,13 +3916,13 @@
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V22">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3934,25 +3934,25 @@
         <v>7.2</v>
       </c>
       <c r="AA22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB22">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AC22">
         <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE22">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG22">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4236,10 +4236,10 @@
         <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
         <v>2.93</v>
@@ -4254,10 +4254,10 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AA24">
         <v>2</v>
@@ -4275,10 +4275,10 @@
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
         <v>1.09</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
         <v>1.5</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="R26">
         <v>1.93</v>
       </c>
       <c r="S26">
+        <v>1.51</v>
+      </c>
+      <c r="T26">
+        <v>2.34</v>
+      </c>
+      <c r="U26">
+        <v>3.3</v>
+      </c>
+      <c r="V26">
+        <v>1.29</v>
+      </c>
+      <c r="W26">
+        <v>1.01</v>
+      </c>
+      <c r="X26">
+        <v>1.08</v>
+      </c>
+      <c r="Y26">
         <v>1.44</v>
       </c>
-      <c r="T26">
-        <v>2.33</v>
-      </c>
-      <c r="U26">
-        <v>3.6</v>
-      </c>
-      <c r="V26">
-        <v>1.25</v>
-      </c>
-      <c r="W26">
-        <v>1.05</v>
-      </c>
-      <c r="X26">
-        <v>1.06</v>
-      </c>
-      <c r="Y26">
-        <v>1.48</v>
-      </c>
       <c r="Z26">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AA26">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AB26">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC26">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD26">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
+        <v>2.7</v>
+      </c>
+      <c r="R27">
+        <v>1.93</v>
+      </c>
+      <c r="S27">
+        <v>1.5</v>
+      </c>
+      <c r="T27">
         <v>2.5</v>
       </c>
-      <c r="R27">
-        <v>2.04</v>
-      </c>
-      <c r="S27">
-        <v>1.51</v>
-      </c>
-      <c r="T27">
-        <v>2.34</v>
-      </c>
       <c r="U27">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z27">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB27">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q2">
         <v>3.55</v>
@@ -656,16 +656,16 @@
         <v>2.85</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
@@ -674,7 +674,7 @@
         <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
         <v>1.85</v>
@@ -683,7 +683,7 @@
         <v>3.37</v>
       </c>
       <c r="AD2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
@@ -692,7 +692,7 @@
         <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
         <v>3</v>
@@ -807,22 +807,22 @@
         <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
         <v>1.06</v>
@@ -831,31 +831,31 @@
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AA3">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AB3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="AD3">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -985,13 +985,13 @@
         <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.24</v>
@@ -1000,25 +1000,25 @@
         <v>3.38</v>
       </c>
       <c r="AA4">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
         <v>3.26</v>
       </c>
       <c r="AD4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
         <v>4.45</v>
@@ -1785,7 +1785,7 @@
         <v>3.5</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
         <v>2.38</v>
@@ -1794,16 +1794,16 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U9">
         <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1815,7 +1815,7 @@
         <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
         <v>2.38</v>
@@ -1827,13 +1827,13 @@
         <v>1.55</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="O24">
         <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -4254,16 +4254,16 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA24">
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
         <v>3.1</v>
@@ -4275,7 +4275,7 @@
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
         <v>2.04</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -641,58 +641,58 @@
         <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
         <v>2.85</v>
       </c>
       <c r="U2">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
         <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC2">
         <v>3.37</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
         <v>1.26</v>
@@ -813,16 +813,16 @@
         <v>1.95</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
         <v>1.06</v>
@@ -834,16 +834,16 @@
         <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AA3">
         <v>2.16</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD3">
         <v>1.16</v>
@@ -855,7 +855,7 @@
         <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>3.75</v>
       </c>
       <c r="P4">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -982,37 +982,37 @@
         <v>3.04</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AA4">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC4">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
         <v>1.9</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O11">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="Q12">
         <v>2.38</v>
@@ -2280,7 +2280,7 @@
         <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
         <v>3.04</v>
@@ -2292,34 +2292,34 @@
         <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>2.85</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
         <v>2.05</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U13">
         <v>2.67</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,16 +2464,16 @@
         <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA13">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC13">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="AD13">
         <v>1.33</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>3.53</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
         <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
         <v>1.09</v>
@@ -2624,31 +2624,31 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
         <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.74</v>
+        <v>7.5</v>
       </c>
       <c r="O19">
-        <v>3.94</v>
+        <v>6.5</v>
       </c>
       <c r="P19">
-        <v>4.11</v>
+        <v>1.33</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,61 +3569,61 @@
         </is>
       </c>
       <c r="N20">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="O20">
-        <v>6.16</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="Q20">
-        <v>6.97</v>
+        <v>2.24</v>
       </c>
       <c r="R20">
-        <v>2.89</v>
+        <v>2.46</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>6.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AD20">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG20">
         <v>2.21</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O21">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U21">
         <v>2.31</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="AA21">
         <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3916,43 +3916,43 @@
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V22">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="W22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z22">
         <v>7.2</v>
       </c>
       <c r="AA22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB22">
         <v>3.2</v>
       </c>
       <c r="AC22">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD22">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AE22">
         <v>1.39</v>
       </c>
       <c r="AF22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
       </c>
       <c r="R24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U24">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
         <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA24">
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
         <v>2.04</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK24">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="O25">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P25">
         <v>3.1</v>
@@ -4396,7 +4396,7 @@
         <v>3.1</v>
       </c>
       <c r="R25">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S25">
         <v>1.53</v>
@@ -4405,43 +4405,43 @@
         <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
         <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y25">
         <v>1.56</v>
       </c>
       <c r="Z25">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA25">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB25">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD25">
         <v>1.13</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q26">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T26">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z26">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA26">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AB26">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD26">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U27">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="Z27">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA27">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD27">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK27">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -635,58 +635,58 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
         <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
         <v>2.85</v>
       </c>
       <c r="U2">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC2">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>1.73</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R3">
         <v>1.95</v>
       </c>
       <c r="S3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="U3">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.04</v>
@@ -837,25 +837,25 @@
         <v>2.57</v>
       </c>
       <c r="AA3">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AB3">
         <v>1.58</v>
       </c>
       <c r="AC3">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
         <v>1.16</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
         <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
         <v>5</v>
@@ -973,52 +973,52 @@
         <v>1.97</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>1.56</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
@@ -1794,13 +1794,13 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="U9">
         <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.08</v>
@@ -1812,7 +1812,7 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
         <v>1.5</v>
@@ -1824,16 +1824,16 @@
         <v>2.23</v>
       </c>
       <c r="AD9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,43 +2102,43 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q11">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
         <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.59</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
         <v>1.83</v>
@@ -2147,20 +2147,20 @@
         <v>1.91</v>
       </c>
       <c r="AC11">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
+        <v>1.9</v>
+      </c>
+      <c r="AG11">
         <v>1.85</v>
       </c>
-      <c r="AG11">
-        <v>1.84</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,16 +2268,16 @@
         <v>1.81</v>
       </c>
       <c r="O12">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
         <v>3.48</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.33</v>
@@ -2298,28 +2298,28 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
         <v>2.05</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
         <v>2.03</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q13">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U13">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AK13">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O14">
+        <v>3.45</v>
+      </c>
+      <c r="P14">
+        <v>3.53</v>
+      </c>
+      <c r="Q14">
+        <v>2.05</v>
+      </c>
+      <c r="R14">
+        <v>2.49</v>
+      </c>
+      <c r="S14">
+        <v>1.28</v>
+      </c>
+      <c r="T14">
         <v>3.5</v>
       </c>
-      <c r="P14">
-        <v>4</v>
-      </c>
-      <c r="Q14">
-        <v>2.26</v>
-      </c>
-      <c r="R14">
-        <v>2.5</v>
-      </c>
-      <c r="S14">
-        <v>1.29</v>
-      </c>
-      <c r="T14">
-        <v>3.22</v>
-      </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
         <v>1.09</v>
@@ -2624,13 +2624,13 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
         <v>2.28</v>
@@ -2645,10 +2645,10 @@
         <v>1.2</v>
       </c>
       <c r="AF14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3409,61 +3409,61 @@
         <v>7.5</v>
       </c>
       <c r="O19">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Q19">
-        <v>6.4</v>
+        <v>6.98</v>
       </c>
       <c r="R19">
         <v>3.09</v>
       </c>
       <c r="S19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="U19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
         <v>1.85</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB19">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC19">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD19">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE19">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AF19">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="AK19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
         <v>2.24</v>
@@ -3590,43 +3590,43 @@
         <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC20">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
         <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC21">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="O22">
         <v>4.8</v>
@@ -3904,22 +3904,22 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R22">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T22">
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V22">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z22">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB22">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AC22">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD22">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AE22">
+        <v>1.35</v>
+      </c>
+      <c r="AF22">
         <v>1.39</v>
       </c>
-      <c r="AF22">
-        <v>1.4</v>
-      </c>
       <c r="AG22">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S24">
         <v>1.38</v>
@@ -4242,43 +4242,43 @@
         <v>2.81</v>
       </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA24">
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
         <v>3.1</v>
@@ -4396,7 +4396,7 @@
         <v>3.1</v>
       </c>
       <c r="R25">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="S25">
         <v>1.53</v>
@@ -4405,13 +4405,13 @@
         <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.1</v>
@@ -4420,16 +4420,16 @@
         <v>1.56</v>
       </c>
       <c r="Z25">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB25">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC25">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD25">
         <v>1.13</v>
@@ -4438,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="AF25">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.44</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,52 +4559,52 @@
         <v>2.7</v>
       </c>
       <c r="R26">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="S26">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="T26">
         <v>2.5</v>
       </c>
       <c r="U26">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.1</v>
       </c>
       <c r="Y26">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AA26">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AB26">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC26">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AD26">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
         <v>2</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,52 +4719,52 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U27">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="AA27">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC27">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD27">
         <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
         <v>1.67</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1462,52 +1462,52 @@
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AC7">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
         <v>2.37</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
         <v>1.36</v>
@@ -2461,31 +2461,31 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
         <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q14">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="S14">
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
         <v>1.56</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
         <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
         <v>2.28</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD14">
         <v>1.52</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG14">
         <v>2.28</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="O19">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>6.98</v>
+        <v>2.24</v>
       </c>
       <c r="R19">
-        <v>3.09</v>
+        <v>2.46</v>
       </c>
       <c r="S19">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>6.55</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC19">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="AD19">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>3.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.05</v>
+        <v>1.99</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="Q20">
-        <v>2.24</v>
+        <v>6.98</v>
       </c>
       <c r="R20">
-        <v>2.46</v>
+        <v>3.09</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>6.55</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>2.19</v>
+        <v>3.4</v>
       </c>
       <c r="AC20">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="AD20">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="AK20">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
         <v>3.3</v>
@@ -4236,7 +4236,7 @@
         <v>2.06</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
         <v>2.81</v>
@@ -4245,40 +4245,40 @@
         <v>2.93</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
         <v>1.06</v>
       </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
         <v>3.4</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB24">
         <v>1.88</v>
       </c>
       <c r="AC24">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R5">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
+        <v>3.01</v>
+      </c>
+      <c r="U5">
+        <v>2.6</v>
+      </c>
+      <c r="V5">
+        <v>1.4</v>
+      </c>
+      <c r="W5">
+        <v>1.08</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.22</v>
+      </c>
+      <c r="Z5">
+        <v>3.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.85</v>
+      </c>
+      <c r="AB5">
+        <v>1.97</v>
+      </c>
+      <c r="AC5">
         <v>2.68</v>
       </c>
-      <c r="U5">
-        <v>2.97</v>
-      </c>
-      <c r="V5">
-        <v>1.34</v>
-      </c>
-      <c r="W5">
-        <v>1.05</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.35</v>
-      </c>
-      <c r="Z5">
-        <v>2.98</v>
-      </c>
-      <c r="AA5">
-        <v>2.05</v>
-      </c>
-      <c r="AB5">
-        <v>1.72</v>
-      </c>
-      <c r="AC5">
-        <v>3.54</v>
-      </c>
       <c r="AD5">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>2.09</v>
+        <v>1.29</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="R6">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="U6">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.84</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R8">
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
         <v>1.1</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
         <v>4.33</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB8">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC8">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
         <v>3.5</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="U9">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AB9">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AC9">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
+        <v>1.12</v>
+      </c>
+      <c r="AF9">
+        <v>1.57</v>
+      </c>
+      <c r="AG9">
+        <v>2.3</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.2</v>
       </c>
-      <c r="AF9">
-        <v>1.45</v>
-      </c>
-      <c r="AG9">
-        <v>2.24</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.18</v>
-      </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA11">
         <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,58 +2265,58 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="P12">
         <v>3.48</v>
       </c>
       <c r="Q12">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
         <v>3.04</v>
       </c>
       <c r="U12">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
         <v>1.73</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
         <v>2.03</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R19">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.27</v>
@@ -3427,10 +3427,10 @@
         <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W19">
         <v>1.1</v>
@@ -3439,31 +3439,31 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
+        <v>1.15</v>
+      </c>
+      <c r="Z19">
+        <v>4.25</v>
+      </c>
+      <c r="AA19">
+        <v>1.58</v>
+      </c>
+      <c r="AB19">
+        <v>2.23</v>
+      </c>
+      <c r="AC19">
+        <v>2.41</v>
+      </c>
+      <c r="AD19">
+        <v>1.47</v>
+      </c>
+      <c r="AE19">
         <v>1.19</v>
-      </c>
-      <c r="Z19">
-        <v>4.33</v>
-      </c>
-      <c r="AA19">
-        <v>1.6</v>
-      </c>
-      <c r="AB19">
-        <v>2.19</v>
-      </c>
-      <c r="AC19">
-        <v>2.42</v>
-      </c>
-      <c r="AD19">
-        <v>1.5</v>
-      </c>
-      <c r="AE19">
-        <v>1.15</v>
       </c>
       <c r="AF19">
         <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>1.26</v>
       </c>
       <c r="Q20">
-        <v>6.98</v>
+        <v>6.25</v>
       </c>
       <c r="R20">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="S20">
         <v>1.14</v>
@@ -3590,13 +3590,13 @@
         <v>4.3</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3614,19 +3614,19 @@
         <v>3.4</v>
       </c>
       <c r="AC20">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD20">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
         <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>3.5</v>
+        <v>1.07</v>
       </c>
       <c r="AK20">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,16 +3735,16 @@
         <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,10 +3753,10 @@
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3765,31 +3765,31 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC21">
         <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>5.49</v>
       </c>
       <c r="Q22">
         <v>1.85</v>
       </c>
       <c r="R22">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="S22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U22">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V22">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z22">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA22">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB22">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AC22">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE22">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AF22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="Q26">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R26">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U26">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V26">
         <v>1.28</v>
       </c>
       <c r="W26">
+        <v>1.01</v>
+      </c>
+      <c r="X26">
+        <v>1.11</v>
+      </c>
+      <c r="Y26">
+        <v>1.43</v>
+      </c>
+      <c r="Z26">
+        <v>2.65</v>
+      </c>
+      <c r="AA26">
+        <v>2.4</v>
+      </c>
+      <c r="AB26">
+        <v>1.5</v>
+      </c>
+      <c r="AC26">
+        <v>4.5</v>
+      </c>
+      <c r="AD26">
+        <v>1.13</v>
+      </c>
+      <c r="AE26">
         <v>1.02</v>
       </c>
-      <c r="X26">
-        <v>1.1</v>
-      </c>
-      <c r="Y26">
-        <v>1.44</v>
-      </c>
-      <c r="Z26">
-        <v>2.43</v>
-      </c>
-      <c r="AA26">
-        <v>2.47</v>
-      </c>
-      <c r="AB26">
-        <v>1.53</v>
-      </c>
-      <c r="AC26">
-        <v>4.45</v>
-      </c>
-      <c r="AD26">
-        <v>1.17</v>
-      </c>
-      <c r="AE26">
-        <v>1.01</v>
-      </c>
       <c r="AF26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG26">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,49 +4719,49 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T27">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="U27">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V27">
         <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="AA27">
         <v>2.35</v>
       </c>
       <c r="AB27">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC27">
         <v>4.25</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>2.05</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
+        <v>1.35</v>
+      </c>
+      <c r="T2">
+        <v>2.99</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
         <v>1.4</v>
       </c>
-      <c r="T2">
-        <v>2.85</v>
-      </c>
-      <c r="U2">
-        <v>2.93</v>
-      </c>
-      <c r="V2">
-        <v>1.37</v>
-      </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.31</v>
@@ -674,10 +674,10 @@
         <v>3.55</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AC2">
         <v>3.4</v>
@@ -686,7 +686,7 @@
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>1.73</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
         <v>1.3</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
+        <v>3.75</v>
+      </c>
+      <c r="P3">
+        <v>5.5</v>
+      </c>
+      <c r="Q3">
+        <v>1.97</v>
+      </c>
+      <c r="R3">
+        <v>2.3</v>
+      </c>
+      <c r="S3">
+        <v>1.36</v>
+      </c>
+      <c r="T3">
+        <v>3.15</v>
+      </c>
+      <c r="U3">
+        <v>2.56</v>
+      </c>
+      <c r="V3">
+        <v>1.38</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.87</v>
+      </c>
+      <c r="AA3">
+        <v>1.85</v>
+      </c>
+      <c r="AB3">
+        <v>1.94</v>
+      </c>
+      <c r="AC3">
         <v>3.1</v>
       </c>
-      <c r="P3">
-        <v>2.75</v>
-      </c>
-      <c r="Q3">
-        <v>3.12</v>
-      </c>
-      <c r="R3">
-        <v>1.95</v>
-      </c>
-      <c r="S3">
-        <v>1.5</v>
-      </c>
-      <c r="T3">
-        <v>2.59</v>
-      </c>
-      <c r="U3">
-        <v>3.3</v>
-      </c>
-      <c r="V3">
-        <v>1.29</v>
-      </c>
-      <c r="W3">
-        <v>1.02</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.4</v>
-      </c>
-      <c r="Z3">
-        <v>2.57</v>
-      </c>
-      <c r="AA3">
-        <v>2.33</v>
-      </c>
-      <c r="AB3">
-        <v>1.58</v>
-      </c>
-      <c r="AC3">
-        <v>4.2</v>
-      </c>
       <c r="AD3">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.3</v>
+      </c>
+      <c r="O4">
+        <v>3.1</v>
+      </c>
+      <c r="P4">
+        <v>2.87</v>
+      </c>
+      <c r="Q4">
+        <v>3.29</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>1.5</v>
+      </c>
+      <c r="T4">
+        <v>2.59</v>
+      </c>
+      <c r="U4">
+        <v>3.3</v>
+      </c>
+      <c r="V4">
+        <v>1.29</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1.09</v>
+      </c>
+      <c r="Y4">
+        <v>1.37</v>
+      </c>
+      <c r="Z4">
+        <v>2.57</v>
+      </c>
+      <c r="AA4">
+        <v>2.33</v>
+      </c>
+      <c r="AB4">
+        <v>1.58</v>
+      </c>
+      <c r="AC4">
+        <v>4.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.16</v>
+      </c>
+      <c r="AE4">
+        <v>1.02</v>
+      </c>
+      <c r="AF4">
+        <v>1.95</v>
+      </c>
+      <c r="AG4">
+        <v>1.76</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.33</v>
+      </c>
+      <c r="AK4">
         <v>1.52</v>
-      </c>
-      <c r="O4">
-        <v>3.9</v>
-      </c>
-      <c r="P4">
-        <v>5</v>
-      </c>
-      <c r="Q4">
-        <v>1.97</v>
-      </c>
-      <c r="R4">
-        <v>2.3</v>
-      </c>
-      <c r="S4">
-        <v>1.36</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>2.54</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>1.22</v>
-      </c>
-      <c r="Z4">
-        <v>3.88</v>
-      </c>
-      <c r="AA4">
-        <v>1.88</v>
-      </c>
-      <c r="AB4">
-        <v>1.94</v>
-      </c>
-      <c r="AC4">
-        <v>3.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.08</v>
-      </c>
-      <c r="AF4">
-        <v>1.9</v>
-      </c>
-      <c r="AG4">
-        <v>1.82</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.2</v>
-      </c>
-      <c r="AK4">
-        <v>2.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="U10">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="V10">
         <v>1.41</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
         <v>1.97</v>
@@ -1987,16 +1987,16 @@
         <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AK10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,19 +2111,19 @@
         <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
         <v>1.4</v>
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AA11">
         <v>1.83</v>
@@ -2150,13 +2150,13 @@
         <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
         <v>1.95</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
         <v>1.97</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P13">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q13">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="U13">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="R14">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
         <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
         <v>1.56</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AC14">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD14">
         <v>1.52</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
         <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.99</v>
+        <v>1.79</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>3.77</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T15">
         <v>2.5</v>
       </c>
       <c r="U15">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AA15">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AD15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.79</v>
+        <v>2.99</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P18">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>3.77</v>
       </c>
       <c r="R18">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="S18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>1.03</v>
       </c>
       <c r="X18">
+        <v>1.08</v>
+      </c>
+      <c r="Y18">
+        <v>1.47</v>
+      </c>
+      <c r="Z18">
+        <v>2.58</v>
+      </c>
+      <c r="AA18">
+        <v>2.5</v>
+      </c>
+      <c r="AB18">
+        <v>1.5</v>
+      </c>
+      <c r="AC18">
+        <v>5</v>
+      </c>
+      <c r="AD18">
+        <v>1.17</v>
+      </c>
+      <c r="AE18">
         <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>1.44</v>
-      </c>
-      <c r="Z18">
-        <v>2.53</v>
-      </c>
-      <c r="AA18">
-        <v>2.35</v>
-      </c>
-      <c r="AB18">
-        <v>1.57</v>
-      </c>
-      <c r="AC18">
-        <v>4.25</v>
-      </c>
-      <c r="AD18">
-        <v>1.15</v>
-      </c>
-      <c r="AE18">
-        <v>1.06</v>
       </c>
       <c r="AF18">
         <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK18">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
         <v>2.18</v>
@@ -3421,46 +3421,46 @@
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
         <v>4.25</v>
       </c>
       <c r="AA19">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB19">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC19">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="AD19">
         <v>1.47</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG19">
         <v>2.25</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>7.5</v>
+        <v>7.65</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -3578,10 +3578,10 @@
         <v>1.26</v>
       </c>
       <c r="Q20">
-        <v>6.25</v>
+        <v>7.22</v>
       </c>
       <c r="R20">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="S20">
         <v>1.14</v>
@@ -3596,7 +3596,7 @@
         <v>1.91</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,10 +3608,10 @@
         <v>6.55</v>
       </c>
       <c r="AA20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
         <v>1.81</v>
@@ -3620,7 +3620,7 @@
         <v>1.95</v>
       </c>
       <c r="AE20">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
         <v>1.55</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="R23">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
         <v>1.23</v>
@@ -4100,13 +4100,13 @@
         <v>1.45</v>
       </c>
       <c r="AB23">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC23">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AD23">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O24">
         <v>3.3</v>
@@ -4230,25 +4230,25 @@
         <v>2.55</v>
       </c>
       <c r="Q24">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
         <v>1.41</v>
       </c>
       <c r="T24">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U24">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.06</v>
@@ -4260,10 +4260,10 @@
         <v>3.4</v>
       </c>
       <c r="AA24">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AC24">
         <v>3.4</v>
@@ -4275,10 +4275,10 @@
         <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,61 +4387,61 @@
         <v>2.3</v>
       </c>
       <c r="O25">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R25">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="U25">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W25">
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y25">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Z25">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA25">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AB25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,55 +4873,55 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="U28">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V28">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
         <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB28">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC28">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AD28">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
@@ -4930,7 +4930,7 @@
         <v>1.45</v>
       </c>
       <c r="AG28">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U15">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z15">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="AB15">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC15">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="AD15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="O16">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>8.25</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R16">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.34</v>
+      </c>
+      <c r="Z16">
+        <v>2.78</v>
+      </c>
+      <c r="AA16">
+        <v>2.08</v>
+      </c>
+      <c r="AB16">
+        <v>1.66</v>
+      </c>
+      <c r="AC16">
+        <v>3.68</v>
+      </c>
+      <c r="AD16">
+        <v>1.2</v>
+      </c>
+      <c r="AE16">
         <v>1.04</v>
       </c>
-      <c r="X16">
+      <c r="AF16">
+        <v>2.57</v>
+      </c>
+      <c r="AG16">
+        <v>1.44</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.07</v>
       </c>
-      <c r="Y16">
-        <v>1.48</v>
-      </c>
-      <c r="Z16">
-        <v>2.33</v>
-      </c>
-      <c r="AA16">
-        <v>2.57</v>
-      </c>
-      <c r="AB16">
-        <v>1.5</v>
-      </c>
-      <c r="AC16">
-        <v>4.9</v>
-      </c>
-      <c r="AD16">
-        <v>1.11</v>
-      </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-      <c r="AF16">
-        <v>2.1</v>
-      </c>
-      <c r="AG16">
-        <v>1.66</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.35</v>
-      </c>
       <c r="AK16">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.35</v>
+        <v>2.99</v>
       </c>
       <c r="O17">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="P17">
-        <v>8.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q17">
+        <v>3.77</v>
+      </c>
+      <c r="R17">
         <v>1.8</v>
       </c>
-      <c r="R17">
-        <v>2.2</v>
-      </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
         <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
         <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="Z17">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="AA17">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC17">
-        <v>3.68</v>
+        <v>5</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE17">
         <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AK17">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.99</v>
+        <v>1.79</v>
       </c>
       <c r="O18">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q18">
-        <v>3.77</v>
+        <v>2.5</v>
       </c>
       <c r="R18">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T18">
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z18">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AA18">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB18">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AD18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
         <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4058,46 +4058,46 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="V23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AA23">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB23">
         <v>2.38</v>
@@ -4106,13 +4106,13 @@
         <v>2.17</v>
       </c>
       <c r="AD23">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AG23">
         <v>2.5</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
         <v>3.1</v>
@@ -4556,7 +4556,7 @@
         <v>3.72</v>
       </c>
       <c r="Q26">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R26">
         <v>1.88</v>
@@ -4586,7 +4586,7 @@
         <v>2.65</v>
       </c>
       <c r="AA26">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB26">
         <v>1.5</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK26">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,16 +4719,16 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R27">
         <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U27">
         <v>3.3</v>
@@ -4737,34 +4737,34 @@
         <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z27">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AA27">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB27">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC27">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD27">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG27">
         <v>1.67</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,22 +4882,22 @@
         <v>2.3</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V28">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W28">
         <v>1.14</v>
@@ -4912,25 +4912,25 @@
         <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB28">
         <v>2.35</v>
       </c>
       <c r="AC28">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AD28">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
         <v>1.45</v>
       </c>
       <c r="AG28">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="O15">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>8.25</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
+        <v>1.03</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.34</v>
+      </c>
+      <c r="Z15">
+        <v>2.78</v>
+      </c>
+      <c r="AA15">
+        <v>2.08</v>
+      </c>
+      <c r="AB15">
+        <v>1.66</v>
+      </c>
+      <c r="AC15">
+        <v>3.68</v>
+      </c>
+      <c r="AD15">
+        <v>1.2</v>
+      </c>
+      <c r="AE15">
         <v>1.04</v>
       </c>
-      <c r="X15">
+      <c r="AF15">
+        <v>2.57</v>
+      </c>
+      <c r="AG15">
+        <v>1.44</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.07</v>
       </c>
-      <c r="Y15">
-        <v>1.48</v>
-      </c>
-      <c r="Z15">
-        <v>2.33</v>
-      </c>
-      <c r="AA15">
-        <v>2.57</v>
-      </c>
-      <c r="AB15">
-        <v>1.5</v>
-      </c>
-      <c r="AC15">
-        <v>4.9</v>
-      </c>
-      <c r="AD15">
-        <v>1.11</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AF15">
-        <v>2.1</v>
-      </c>
-      <c r="AG15">
-        <v>1.66</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.35</v>
-      </c>
       <c r="AK15">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>8.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q16">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T16">
         <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z16">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="AA16">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB16">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC16">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="AD16">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P18">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R18">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="S18">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y18">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z18">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="AA18">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC18">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="AD18">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE18">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK18">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P25">
         <v>3.4</v>
@@ -4399,22 +4399,22 @@
         <v>1.76</v>
       </c>
       <c r="S25">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U25">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y25">
         <v>1.53</v>
@@ -4426,7 +4426,7 @@
         <v>2.56</v>
       </c>
       <c r="AB25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
@@ -4435,13 +4435,13 @@
         <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF25">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1127,22 +1127,22 @@
         <v>3.2</v>
       </c>
       <c r="O5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S5">
         <v>1.34</v>
       </c>
       <c r="T5">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="U5">
         <v>2.6</v>
@@ -1154,7 +1154,7 @@
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
@@ -1163,41 +1163,41 @@
         <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB5">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
         <v>1.09</v>
       </c>
       <c r="AF5">
+        <v>1.62</v>
+      </c>
+      <c r="AG5">
+        <v>2.12</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.65</v>
       </c>
-      <c r="AG5">
-        <v>2.1</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.29</v>
-      </c>
       <c r="AK5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="Q6">
         <v>2.28</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
         <v>2.04</v>
@@ -1462,19 +1462,19 @@
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
         <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC7">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
         <v>1.1</v>
@@ -1646,16 +1646,16 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
         <v>4.33</v>
       </c>
       <c r="AA8">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC8">
         <v>2.56</v>
@@ -1670,7 +1670,7 @@
         <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.7</v>
       </c>
       <c r="AK8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -1806,19 +1806,19 @@
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
         <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
         <v>2.63</v>
@@ -1849,7 +1849,7 @@
         <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>3.67</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="U10">
         <v>2.59</v>
@@ -1975,28 +1975,28 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
         <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
         <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
         <v>1.33</v>
@@ -2108,10 +2108,10 @@
         <v>3.8</v>
       </c>
       <c r="P11">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="R11">
         <v>2.2</v>
@@ -2120,10 +2120,10 @@
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="V11">
         <v>1.4</v>
@@ -2132,25 +2132,25 @@
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.34</v>
+        <v>3.53</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB11">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>3.31</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="Q12">
         <v>2.38</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.04</v>
       </c>
       <c r="Y12">
+        <v>1.19</v>
+      </c>
+      <c r="Z12">
+        <v>3.8</v>
+      </c>
+      <c r="AA12">
+        <v>1.77</v>
+      </c>
+      <c r="AB12">
+        <v>1.95</v>
+      </c>
+      <c r="AC12">
+        <v>2.8</v>
+      </c>
+      <c r="AD12">
+        <v>1.39</v>
+      </c>
+      <c r="AE12">
+        <v>1.13</v>
+      </c>
+      <c r="AF12">
+        <v>1.7</v>
+      </c>
+      <c r="AG12">
+        <v>2.15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.25</v>
       </c>
-      <c r="Z12">
-        <v>3.86</v>
-      </c>
-      <c r="AA12">
-        <v>1.75</v>
-      </c>
-      <c r="AB12">
-        <v>2.05</v>
-      </c>
-      <c r="AC12">
-        <v>2.9</v>
-      </c>
-      <c r="AD12">
-        <v>1.33</v>
-      </c>
-      <c r="AE12">
-        <v>1.08</v>
-      </c>
-      <c r="AF12">
-        <v>1.73</v>
-      </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.28</v>
-      </c>
       <c r="AK12">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2757,58 +2757,58 @@
         <v>1.35</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="P15">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="Q15">
         <v>1.8</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA15">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AG15">
         <v>1.44</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
         <v>3</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q16">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R16">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T16">
         <v>2.5</v>
       </c>
       <c r="U16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2950,31 +2950,31 @@
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AA16">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AB16">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC16">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD16">
         <v>1.15</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
         <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="O17">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="R17">
         <v>1.8</v>
       </c>
       <c r="S17">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="U17">
         <v>3.5</v>
@@ -3107,19 +3107,19 @@
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y17">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z17">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AA17">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB17">
         <v>1.5</v>
@@ -3131,10 +3131,10 @@
         <v>1.17</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG17">
         <v>1.67</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AK17">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3249,19 +3249,19 @@
         <v>2.7</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
       </c>
       <c r="R18">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S18">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T18">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U18">
         <v>3.5</v>
@@ -3273,34 +3273,34 @@
         <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y18">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z18">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AA18">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AB18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC18">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD18">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE18">
         <v>1</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG18">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q19">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S19">
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
         <v>2.21</v>
       </c>
       <c r="AC19">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AD19">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
         <v>2.25</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>7.65</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P20">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q20">
-        <v>7.22</v>
+        <v>6.7</v>
       </c>
       <c r="R20">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="S20">
         <v>1.14</v>
@@ -3590,13 +3590,13 @@
         <v>4.3</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,28 +3605,28 @@
         <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>6.55</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="AC20">
         <v>1.81</v>
       </c>
       <c r="AD20">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AF20">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="P21">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q21">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
         <v>2.3</v>
       </c>
       <c r="AC21">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O22">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P22">
-        <v>5.49</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>1.85</v>
       </c>
       <c r="R22">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T22">
         <v>4.8</v>
       </c>
       <c r="U22">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V22">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AB22">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AC22">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG22">
         <v>2.7</v>
@@ -3968,7 +3968,7 @@
         <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O23">
         <v>3.6</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -4079,7 +4079,7 @@
         <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V23">
         <v>1.62</v>
@@ -4094,22 +4094,22 @@
         <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA23">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC23">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
         <v>1.62</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF23">
         <v>1.42</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
         <v>3.3</v>
@@ -4233,40 +4233,40 @@
         <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="U24">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB24">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
         <v>1.28</v>
@@ -4275,10 +4275,10 @@
         <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>3.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q26">
         <v>2.7</v>
@@ -4580,22 +4580,22 @@
         <v>1.11</v>
       </c>
       <c r="Y26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AA26">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB26">
         <v>1.5</v>
       </c>
       <c r="AC26">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE26">
         <v>1.02</v>
@@ -4719,16 +4719,16 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U27">
         <v>3.3</v>
@@ -4746,7 +4746,7 @@
         <v>1.46</v>
       </c>
       <c r="Z27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AA27">
         <v>2.38</v>
@@ -4758,13 +4758,13 @@
         <v>4.3</v>
       </c>
       <c r="AD27">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
         <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG27">
         <v>1.67</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
         <v>1.78</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q28">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U28">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V28">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W28">
         <v>1.14</v>
@@ -4909,28 +4909,28 @@
         <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA28">
         <v>1.55</v>
       </c>
       <c r="AB28">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD28">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.07</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>2.9</v>
+      </c>
+      <c r="Q2">
+        <v>3.25</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>1.48</v>
+      </c>
+      <c r="T2">
+        <v>2.38</v>
+      </c>
+      <c r="U2">
         <v>3.2</v>
       </c>
-      <c r="P2">
-        <v>2.11</v>
-      </c>
-      <c r="Q2">
-        <v>3.45</v>
-      </c>
-      <c r="R2">
-        <v>2.2</v>
-      </c>
-      <c r="S2">
-        <v>1.35</v>
-      </c>
-      <c r="T2">
-        <v>2.99</v>
-      </c>
-      <c r="U2">
-        <v>2.63</v>
-      </c>
       <c r="V2">
+        <v>1.3</v>
+      </c>
+      <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
+        <v>1.04</v>
+      </c>
+      <c r="Y2">
         <v>1.4</v>
       </c>
-      <c r="W2">
+      <c r="Z2">
+        <v>2.61</v>
+      </c>
+      <c r="AA2">
+        <v>2.31</v>
+      </c>
+      <c r="AB2">
+        <v>1.58</v>
+      </c>
+      <c r="AC2">
+        <v>4.64</v>
+      </c>
+      <c r="AD2">
+        <v>1.16</v>
+      </c>
+      <c r="AE2">
         <v>1.03</v>
       </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
-      <c r="Y2">
-        <v>1.31</v>
-      </c>
-      <c r="Z2">
-        <v>3.55</v>
-      </c>
-      <c r="AA2">
-        <v>1.82</v>
-      </c>
-      <c r="AB2">
-        <v>1.79</v>
-      </c>
-      <c r="AC2">
-        <v>3.4</v>
-      </c>
-      <c r="AD2">
-        <v>1.29</v>
-      </c>
-      <c r="AE2">
-        <v>1.12</v>
-      </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>5.81</v>
       </c>
       <c r="Q3">
         <v>1.97</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
+        <v>1.11</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.2</v>
+      </c>
+      <c r="Z3">
+        <v>3.95</v>
+      </c>
+      <c r="AA3">
+        <v>1.72</v>
+      </c>
+      <c r="AB3">
+        <v>2.2</v>
+      </c>
+      <c r="AC3">
+        <v>2.75</v>
+      </c>
+      <c r="AD3">
+        <v>1.35</v>
+      </c>
+      <c r="AE3">
+        <v>1.11</v>
+      </c>
+      <c r="AF3">
+        <v>1.9</v>
+      </c>
+      <c r="AG3">
+        <v>1.83</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.08</v>
       </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.87</v>
-      </c>
-      <c r="AA3">
-        <v>1.85</v>
-      </c>
-      <c r="AB3">
-        <v>1.94</v>
-      </c>
-      <c r="AC3">
-        <v>3.1</v>
-      </c>
-      <c r="AD3">
-        <v>1.38</v>
-      </c>
-      <c r="AE3">
-        <v>1.08</v>
-      </c>
-      <c r="AF3">
-        <v>1.88</v>
-      </c>
-      <c r="AG3">
-        <v>1.82</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.2</v>
-      </c>
       <c r="AK3">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.87</v>
+        <v>2.13</v>
       </c>
       <c r="Q4">
-        <v>3.29</v>
+        <v>3.7</v>
       </c>
       <c r="R4">
+        <v>2.06</v>
+      </c>
+      <c r="S4">
+        <v>1.41</v>
+      </c>
+      <c r="T4">
+        <v>2.75</v>
+      </c>
+      <c r="U4">
+        <v>2.63</v>
+      </c>
+      <c r="V4">
+        <v>1.36</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.26</v>
+      </c>
+      <c r="Z4">
+        <v>3.25</v>
+      </c>
+      <c r="AA4">
+        <v>1.94</v>
+      </c>
+      <c r="AB4">
+        <v>1.83</v>
+      </c>
+      <c r="AC4">
+        <v>3.3</v>
+      </c>
+      <c r="AD4">
+        <v>1.25</v>
+      </c>
+      <c r="AE4">
+        <v>1.12</v>
+      </c>
+      <c r="AF4">
+        <v>1.73</v>
+      </c>
+      <c r="AG4">
         <v>2</v>
       </c>
-      <c r="S4">
-        <v>1.5</v>
-      </c>
-      <c r="T4">
-        <v>2.59</v>
-      </c>
-      <c r="U4">
-        <v>3.3</v>
-      </c>
-      <c r="V4">
-        <v>1.29</v>
-      </c>
-      <c r="W4">
-        <v>1.02</v>
-      </c>
-      <c r="X4">
-        <v>1.09</v>
-      </c>
-      <c r="Y4">
-        <v>1.37</v>
-      </c>
-      <c r="Z4">
-        <v>2.57</v>
-      </c>
-      <c r="AA4">
-        <v>2.33</v>
-      </c>
-      <c r="AB4">
-        <v>1.58</v>
-      </c>
-      <c r="AC4">
-        <v>4.2</v>
-      </c>
-      <c r="AD4">
-        <v>1.16</v>
-      </c>
-      <c r="AE4">
-        <v>1.02</v>
-      </c>
-      <c r="AF4">
-        <v>1.95</v>
-      </c>
-      <c r="AG4">
-        <v>1.76</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK4">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="O13">
         <v>3.15</v>
       </c>
       <c r="P13">
+        <v>2.3</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
         <v>2.25</v>
       </c>
-      <c r="Q13">
-        <v>3.1</v>
-      </c>
-      <c r="R13">
-        <v>2.12</v>
-      </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V13">
         <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC13">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
+        <v>1.55</v>
+      </c>
+      <c r="AG13">
+        <v>2.38</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.62</v>
       </c>
-      <c r="AG13">
-        <v>2.23</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.24</v>
-      </c>
       <c r="AK13">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>3.53</v>
+        <v>3.95</v>
       </c>
       <c r="Q14">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
+        <v>2.4</v>
+      </c>
+      <c r="S14">
+        <v>1.25</v>
+      </c>
+      <c r="T14">
+        <v>3.2</v>
+      </c>
+      <c r="U14">
         <v>2.25</v>
-      </c>
-      <c r="S14">
-        <v>1.29</v>
-      </c>
-      <c r="T14">
-        <v>3.4</v>
-      </c>
-      <c r="U14">
-        <v>2.23</v>
       </c>
       <c r="V14">
         <v>1.56</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AB14">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AD14">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE14">
+        <v>1.25</v>
+      </c>
+      <c r="AF14">
+        <v>1.55</v>
+      </c>
+      <c r="AG14">
+        <v>2.37</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.21</v>
       </c>
-      <c r="AF14">
-        <v>1.56</v>
-      </c>
-      <c r="AG14">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.15</v>
-      </c>
       <c r="AK14">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>2.25</v>
       </c>
       <c r="O25">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
       </c>
       <c r="R25">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S25">
         <v>1.53</v>
@@ -4405,25 +4405,25 @@
         <v>2.13</v>
       </c>
       <c r="U25">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X25">
         <v>1.08</v>
       </c>
       <c r="Y25">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z25">
         <v>2.3</v>
       </c>
       <c r="AA25">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AB25">
         <v>1.42</v>
@@ -4441,7 +4441,7 @@
         <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2">
@@ -631,111 +631,111 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
+        <v>3.3</v>
+      </c>
+      <c r="P2">
+        <v>2.13</v>
+      </c>
+      <c r="Q2">
+        <v>3.7</v>
+      </c>
+      <c r="R2">
+        <v>2.06</v>
+      </c>
+      <c r="S2">
+        <v>1.41</v>
+      </c>
+      <c r="T2">
+        <v>2.75</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>1.36</v>
+      </c>
+      <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.26</v>
+      </c>
+      <c r="Z2">
+        <v>3.25</v>
+      </c>
+      <c r="AA2">
+        <v>1.94</v>
+      </c>
+      <c r="AB2">
+        <v>1.83</v>
+      </c>
+      <c r="AC2">
+        <v>3.3</v>
+      </c>
+      <c r="AD2">
+        <v>1.25</v>
+      </c>
+      <c r="AE2">
+        <v>1.12</v>
+      </c>
+      <c r="AF2">
+        <v>1.73</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.67</v>
+      </c>
+      <c r="AK2">
+        <v>1.26</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>2</v>
+      </c>
+      <c r="AO2">
         <v>3</v>
       </c>
-      <c r="P2">
-        <v>2.9</v>
-      </c>
-      <c r="Q2">
-        <v>3.25</v>
-      </c>
-      <c r="R2">
+      <c r="AP2">
         <v>2</v>
       </c>
-      <c r="S2">
-        <v>1.48</v>
-      </c>
-      <c r="T2">
-        <v>2.38</v>
-      </c>
-      <c r="U2">
-        <v>3.2</v>
-      </c>
-      <c r="V2">
-        <v>1.3</v>
-      </c>
-      <c r="W2">
-        <v>1.02</v>
-      </c>
-      <c r="X2">
-        <v>1.04</v>
-      </c>
-      <c r="Y2">
-        <v>1.4</v>
-      </c>
-      <c r="Z2">
-        <v>2.61</v>
-      </c>
-      <c r="AA2">
-        <v>2.31</v>
-      </c>
-      <c r="AB2">
-        <v>1.58</v>
-      </c>
-      <c r="AC2">
-        <v>4.64</v>
-      </c>
-      <c r="AD2">
-        <v>1.16</v>
-      </c>
-      <c r="AE2">
-        <v>1.03</v>
-      </c>
-      <c r="AF2">
-        <v>1.93</v>
-      </c>
-      <c r="AG2">
-        <v>1.75</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.33</v>
-      </c>
-      <c r="AK2">
-        <v>1.5</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>-1</v>
-      </c>
-      <c r="AN2">
-        <v>-1</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>-1</v>
-      </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -929,139 +929,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.4</v>
+      </c>
+      <c r="Z4">
+        <v>2.61</v>
+      </c>
+      <c r="AA4">
+        <v>2.31</v>
+      </c>
+      <c r="AB4">
+        <v>1.58</v>
+      </c>
+      <c r="AC4">
+        <v>4.64</v>
+      </c>
+      <c r="AD4">
+        <v>1.16</v>
+      </c>
+      <c r="AE4">
         <v>1.03</v>
       </c>
-      <c r="Y4">
-        <v>1.26</v>
-      </c>
-      <c r="Z4">
-        <v>3.25</v>
-      </c>
-      <c r="AA4">
-        <v>1.94</v>
-      </c>
-      <c r="AB4">
-        <v>1.83</v>
-      </c>
-      <c r="AC4">
-        <v>3.3</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.12</v>
-      </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["90+1"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>["15", "49"]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.33</v>
+      </c>
+      <c r="AK4">
+        <v>1.5</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>2</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.67</v>
-      </c>
-      <c r="AK4">
-        <v>1.26</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.77</v>
+        <v>3.3</v>
       </c>
       <c r="O16">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="R16">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S16">
+        <v>1.56</v>
+      </c>
+      <c r="T16">
+        <v>2.26</v>
+      </c>
+      <c r="U16">
+        <v>3.5</v>
+      </c>
+      <c r="V16">
+        <v>1.25</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>1.11</v>
+      </c>
+      <c r="Y16">
         <v>1.5</v>
       </c>
-      <c r="T16">
-        <v>2.5</v>
-      </c>
-      <c r="U16">
-        <v>3.3</v>
-      </c>
-      <c r="V16">
-        <v>1.29</v>
-      </c>
-      <c r="W16">
-        <v>1.03</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.4</v>
-      </c>
       <c r="Z16">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA16">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AB16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG16">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
+        <v>1.77</v>
+      </c>
+      <c r="O17">
+        <v>3.15</v>
+      </c>
+      <c r="P17">
+        <v>4.1</v>
+      </c>
+      <c r="Q17">
+        <v>2.47</v>
+      </c>
+      <c r="R17">
+        <v>1.93</v>
+      </c>
+      <c r="S17">
+        <v>1.5</v>
+      </c>
+      <c r="T17">
+        <v>2.5</v>
+      </c>
+      <c r="U17">
         <v>3.3</v>
       </c>
-      <c r="O17">
+      <c r="V17">
+        <v>1.29</v>
+      </c>
+      <c r="W17">
+        <v>1.03</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.4</v>
+      </c>
+      <c r="Z17">
         <v>2.75</v>
       </c>
-      <c r="P17">
-        <v>2.3</v>
-      </c>
-      <c r="Q17">
-        <v>4.33</v>
-      </c>
-      <c r="R17">
-        <v>1.8</v>
-      </c>
-      <c r="S17">
-        <v>1.56</v>
-      </c>
-      <c r="T17">
-        <v>2.26</v>
-      </c>
-      <c r="U17">
-        <v>3.5</v>
-      </c>
-      <c r="V17">
+      <c r="AA17">
+        <v>2.18</v>
+      </c>
+      <c r="AB17">
+        <v>1.55</v>
+      </c>
+      <c r="AC17">
+        <v>4.5</v>
+      </c>
+      <c r="AD17">
+        <v>1.15</v>
+      </c>
+      <c r="AE17">
+        <v>1.01</v>
+      </c>
+      <c r="AF17">
+        <v>2.05</v>
+      </c>
+      <c r="AG17">
+        <v>1.71</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.25</v>
       </c>
-      <c r="W17">
-        <v>1.04</v>
-      </c>
-      <c r="X17">
-        <v>1.11</v>
-      </c>
-      <c r="Y17">
-        <v>1.5</v>
-      </c>
-      <c r="Z17">
-        <v>2.63</v>
-      </c>
-      <c r="AA17">
-        <v>2.4</v>
-      </c>
-      <c r="AB17">
-        <v>1.5</v>
-      </c>
-      <c r="AC17">
-        <v>5</v>
-      </c>
-      <c r="AD17">
-        <v>1.17</v>
-      </c>
-      <c r="AE17">
-        <v>1.02</v>
-      </c>
-      <c r="AF17">
-        <v>2.04</v>
-      </c>
-      <c r="AG17">
-        <v>1.67</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.5</v>
-      </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1130,58 +1130,58 @@
         <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q5">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R5">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA5">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
         <v>1.3</v>
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1276,39 +1276,39 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Q6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="U6">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
         <v>1.33</v>
@@ -1317,77 +1317,77 @@
         <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
         <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>["86"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,130 +1427,130 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
         <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
         <v>1.96</v>
       </c>
       <c r="AC7">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "27", "70"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "48"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,36 +1602,36 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>4.14</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U8">
         <v>2.4</v>
@@ -1640,80 +1640,80 @@
         <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="AA8">
         <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AC8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
-        <v>3.67</v>
+        <v>3.22</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
         <v>2.59</v>
@@ -1969,31 +1969,31 @@
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
         <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
         <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
         <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
         <v>2.1</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AK10">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,61 +2102,61 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q11">
+        <v>2.37</v>
+      </c>
+      <c r="R11">
         <v>2.17</v>
       </c>
-      <c r="R11">
-        <v>2.2</v>
-      </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="AA11">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
         <v>1.95</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="O13">
         <v>3.15</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U13">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="V13">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AB13">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
         <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
         <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2627,28 +2627,28 @@
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
         <v>1.54</v>
       </c>
       <c r="AB14">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="AD14">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O15">
         <v>3.78</v>
       </c>
       <c r="P15">
-        <v>9.75</v>
+        <v>8.75</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,61 +2917,61 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>4.33</v>
+        <v>2.37</v>
       </c>
       <c r="R16">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="S16">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="T16">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W16">
+        <v>1.01</v>
+      </c>
+      <c r="X16">
         <v>1.04</v>
       </c>
-      <c r="X16">
-        <v>1.11</v>
-      </c>
       <c r="Y16">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z16">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AA16">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AB16">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD16">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
         <v>1.67</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="P17">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="S17">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U17">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
         <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z17">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA17">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AB17">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AC17">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD17">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE17">
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P18">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>3.4</v>
+        <v>4.49</v>
       </c>
       <c r="R18">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="S18">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T18">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U18">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V18">
         <v>1.22</v>
@@ -3273,34 +3273,34 @@
         <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z18">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AA18">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AB18">
         <v>1.44</v>
       </c>
       <c r="AC18">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AG18">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AK18">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="Q19">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
         <v>3.6</v>
@@ -3433,10 +3433,10 @@
         <v>1.55</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.15</v>
@@ -3448,19 +3448,19 @@
         <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AC19">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
         <v>2.25</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="P20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q20">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="R20">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
         <v>4.3</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="AC20">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AD20">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AE20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF20">
         <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-08-25.xlsx
+++ b/jogos_2026-08-25.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,118 +1765,118 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q9">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="R9">
         <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA9">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
         <v>2.63</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["77"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,130 +2242,130 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="R12">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.2</v>
+      </c>
+      <c r="Z12">
+        <v>3.96</v>
+      </c>
+      <c r="AA12">
+        <v>1.72</v>
+      </c>
+      <c r="AB12">
+        <v>2.07</v>
+      </c>
+      <c r="AC12">
+        <v>2.71</v>
+      </c>
+      <c r="AD12">
+        <v>1.36</v>
+      </c>
+      <c r="AE12">
         <v>1.1</v>
       </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.19</v>
-      </c>
-      <c r="Z12">
-        <v>3.8</v>
-      </c>
-      <c r="AA12">
-        <v>1.77</v>
-      </c>
-      <c r="AB12">
-        <v>1.95</v>
-      </c>
-      <c r="AC12">
-        <v>2.8</v>
-      </c>
-      <c r="AD12">
-        <v>1.39</v>
-      </c>
-      <c r="AE12">
-        <v>1.13</v>
-      </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["101", "115", "38", "74", "90+4"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "61"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,11 +2420,11 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "45"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,16 +2507,16 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "62"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,139 +2885,139 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
+        <v>2.8</v>
+      </c>
+      <c r="P16">
+        <v>2.87</v>
+      </c>
+      <c r="Q16">
         <v>3.2</v>
       </c>
-      <c r="P16">
-        <v>3.55</v>
-      </c>
-      <c r="Q16">
-        <v>2.37</v>
-      </c>
       <c r="R16">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="S16">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="T16">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="U16">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="V16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Z16">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AA16">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AB16">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AC16">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="AD16">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "74"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "49", "60"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,19 +3048,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3069,118 +3069,118 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2.87</v>
+        <v>3.55</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="R17">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="T17">
+        <v>2.62</v>
+      </c>
+      <c r="U17">
+        <v>3.25</v>
+      </c>
+      <c r="V17">
+        <v>1.27</v>
+      </c>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.44</v>
+      </c>
+      <c r="Z17">
+        <v>2.56</v>
+      </c>
+      <c r="AA17">
         <v>2.18</v>
       </c>
-      <c r="U17">
-        <v>3.45</v>
-      </c>
-      <c r="V17">
-        <v>1.25</v>
-      </c>
-      <c r="W17">
-        <v>1.03</v>
-      </c>
-      <c r="X17">
-        <v>1.07</v>
-      </c>
-      <c r="Y17">
-        <v>1.52</v>
-      </c>
-      <c r="Z17">
-        <v>2.55</v>
-      </c>
-      <c r="AA17">
-        <v>2.55</v>
-      </c>
       <c r="AB17">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AC17">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="AD17">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE17">
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3223,23 +3223,23 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "50"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "45+1", "81"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "41", "57"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P21">
         <v>3.46</v>
       </c>
       <c r="Q21">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R21">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>5.81</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD21">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE21">
+        <v>1.24</v>
+      </c>
+      <c r="AF21">
+        <v>1.44</v>
+      </c>
+      <c r="AG21">
+        <v>2.62</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.22</v>
       </c>
-      <c r="AF21">
-        <v>1.49</v>
-      </c>
-      <c r="AG21">
-        <v>2.5</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
       <c r="AK21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,28 +3898,28 @@
         <v>1.52</v>
       </c>
       <c r="O22">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R22">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S22">
         <v>1.15</v>
       </c>
       <c r="T22">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="U22">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V22">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -3928,25 +3928,25 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB22">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AC22">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4079,7 +4079,7 @@
         <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V23">
         <v>1.62</v>
@@ -4088,50 +4088,50 @@
         <v>1.17</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AA23">
         <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AC23">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AD23">
         <v>1.62</v>
       </c>
       <c r="AE23">
+        <v>1.22</v>
+      </c>
+      <c r="AF23">
+        <v>1.45</v>
+      </c>
+      <c r="AG23">
+        <v>2.45</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="AF23">
-        <v>1.42</v>
-      </c>
-      <c r="AG23">
-        <v>2.5</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.22</v>
-      </c>
       <c r="AK23">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R24">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="U24">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.36</v>
+      </c>
+      <c r="Z24">
+        <v>3.1</v>
+      </c>
+      <c r="AA24">
+        <v>2.02</v>
+      </c>
+      <c r="AB24">
+        <v>1.72</v>
+      </c>
+      <c r="AC24">
+        <v>3.8</v>
+      </c>
+      <c r="AD24">
+        <v>1.23</v>
+      </c>
+      <c r="AE24">
         <v>1.03</v>
       </c>
-      <c r="Y24">
-        <v>1.32</v>
-      </c>
-      <c r="Z24">
-        <v>3.5</v>
-      </c>
-      <c r="AA24">
-        <v>1.92</v>
-      </c>
-      <c r="AB24">
-        <v>1.85</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.28</v>
-      </c>
-      <c r="AE24">
-        <v>1.06</v>
-      </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P25">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q25">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S25">
         <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="U25">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
         <v>1</v>
@@ -4417,22 +4417,22 @@
         <v>1.08</v>
       </c>
       <c r="Y25">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z25">
         <v>2.3</v>
       </c>
       <c r="AA25">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AB25">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE25">
         <v>1</v>
@@ -4441,7 +4441,7 @@
         <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,43 +4547,43 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
         <v>3</v>
       </c>
       <c r="P26">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
         <v>2.7</v>
       </c>
       <c r="R26">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T26">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="U26">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y26">
         <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA26">
         <v>2.5</v>
@@ -4592,35 +4592,35 @@
         <v>1.5</v>
       </c>
       <c r="AC26">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD26">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
+        <v>1.7</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.33</v>
+      </c>
+      <c r="AK26">
         <v>1.67</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.34</v>
-      </c>
-      <c r="AK26">
-        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="R27">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="U27">
         <v>3.3</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z27">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AA27">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AB27">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC27">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
         <v>2.03</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
         <v>3.12</v>
@@ -4900,31 +4900,31 @@
         <v>1.55</v>
       </c>
       <c r="W28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AC28">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE28">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
         <v>1.47</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK28">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL28">
         <v>0</v>
